--- a/artfynd/A 46597-2024 artfynd.xlsx
+++ b/artfynd/A 46597-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120804435</v>
       </c>
       <c r="B2" t="n">
-        <v>74644</v>
+        <v>74647</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>120804297</v>
       </c>
       <c r="B3" t="n">
-        <v>56560</v>
+        <v>56563</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>121150212</v>
       </c>
       <c r="B4" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 46597-2024 artfynd.xlsx
+++ b/artfynd/A 46597-2024 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>121150212</v>
       </c>
       <c r="B4" t="n">
-        <v>92008</v>
+        <v>92020</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 46597-2024 artfynd.xlsx
+++ b/artfynd/A 46597-2024 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>121150212</v>
       </c>
       <c r="B4" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 46597-2024 artfynd.xlsx
+++ b/artfynd/A 46597-2024 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>121150212</v>
       </c>
       <c r="B4" t="n">
-        <v>92021</v>
+        <v>92024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
